--- a/artfynd/A 40464-2024 artfynd.xlsx
+++ b/artfynd/A 40464-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120203880</v>
+        <v>120204035</v>
       </c>
       <c r="B2" t="n">
-        <v>90562</v>
+        <v>57310</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566742</v>
+        <v>566792</v>
       </c>
       <c r="R2" t="n">
-        <v>7040625</v>
+        <v>7040454</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,22 +780,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120204669</v>
+        <v>120204829</v>
       </c>
       <c r="B3" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +808,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566938</v>
+        <v>566806</v>
       </c>
       <c r="R3" t="n">
-        <v>7040521</v>
+        <v>7040686</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,12 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:36</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120204731</v>
+        <v>120203108</v>
       </c>
       <c r="B4" t="n">
-        <v>90527</v>
+        <v>97907</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,38 +916,42 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566899</v>
+        <v>566673</v>
       </c>
       <c r="R4" t="n">
-        <v>7040617</v>
+        <v>7040645</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +993,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,22 +1008,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120204481</v>
+        <v>120204350</v>
       </c>
       <c r="B5" t="n">
-        <v>78526</v>
+        <v>91005</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1028,25 +1032,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1056,10 +1060,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566855</v>
+        <v>566788</v>
       </c>
       <c r="R5" t="n">
-        <v>7040571</v>
+        <v>7040610</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,7 +1095,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1105,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,10 +1132,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120203518</v>
+        <v>120204731</v>
       </c>
       <c r="B6" t="n">
-        <v>56514</v>
+        <v>90527</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1140,43 +1144,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102612</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566701</v>
+        <v>566899</v>
       </c>
       <c r="R6" t="n">
-        <v>7040656</v>
+        <v>7040617</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1208,7 +1207,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1217,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1233,12 +1232,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1362,10 +1361,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120204246</v>
+        <v>120203518</v>
       </c>
       <c r="B8" t="n">
-        <v>97907</v>
+        <v>56514</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1374,30 +1373,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1406,10 +1406,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566744</v>
+        <v>566701</v>
       </c>
       <c r="R8" t="n">
-        <v>7040571</v>
+        <v>7040656</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1441,7 +1441,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1478,10 +1478,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120203108</v>
+        <v>120204143</v>
       </c>
       <c r="B9" t="n">
-        <v>97907</v>
+        <v>57326</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1490,30 +1490,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>5</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1522,10 +1523,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>566673</v>
+        <v>566773</v>
       </c>
       <c r="R9" t="n">
-        <v>7040645</v>
+        <v>7040502</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1557,7 +1558,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1567,7 +1568,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1582,22 +1583,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120203415</v>
+        <v>120203880</v>
       </c>
       <c r="B10" t="n">
-        <v>82305</v>
+        <v>90562</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1610,21 +1611,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1634,10 +1635,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566663</v>
+        <v>566742</v>
       </c>
       <c r="R10" t="n">
-        <v>7040644</v>
+        <v>7040625</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1669,7 +1670,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1679,7 +1680,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1706,10 +1707,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120204419</v>
+        <v>120203415</v>
       </c>
       <c r="B11" t="n">
-        <v>57310</v>
+        <v>82305</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1722,39 +1723,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566839</v>
+        <v>566663</v>
       </c>
       <c r="R11" t="n">
-        <v>7040579</v>
+        <v>7040644</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1786,7 +1782,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1796,7 +1792,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1811,19 +1807,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120203654</v>
+        <v>120204501</v>
       </c>
       <c r="B12" t="n">
         <v>57310</v>
@@ -1857,21 +1853,16 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566693</v>
+        <v>566856</v>
       </c>
       <c r="R12" t="n">
-        <v>7040577</v>
+        <v>7040544</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1903,7 +1894,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1913,12 +1904,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1933,22 +1924,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120204501</v>
+        <v>120204246</v>
       </c>
       <c r="B13" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1957,38 +1948,42 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566856</v>
+        <v>566744</v>
       </c>
       <c r="R13" t="n">
-        <v>7040544</v>
+        <v>7040571</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2020,7 +2015,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2030,12 +2025,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:25</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2062,10 +2052,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120204174</v>
+        <v>120204481</v>
       </c>
       <c r="B14" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2074,42 +2064,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566744</v>
+        <v>566855</v>
       </c>
       <c r="R14" t="n">
-        <v>7040575</v>
+        <v>7040571</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2141,7 +2127,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2151,7 +2137,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2290,10 +2276,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120203772</v>
+        <v>120204371</v>
       </c>
       <c r="B16" t="n">
-        <v>57326</v>
+        <v>90562</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2306,39 +2292,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>566730</v>
+        <v>566783</v>
       </c>
       <c r="R16" t="n">
-        <v>7040540</v>
+        <v>7040615</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2370,7 +2351,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2380,7 +2361,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2395,22 +2376,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120204747</v>
+        <v>120203772</v>
       </c>
       <c r="B17" t="n">
-        <v>78526</v>
+        <v>57326</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2423,34 +2404,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>566894</v>
+        <v>566730</v>
       </c>
       <c r="R17" t="n">
-        <v>7040615</v>
+        <v>7040540</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2482,7 +2468,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2492,7 +2478,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2507,19 +2493,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120204371</v>
+        <v>120204659</v>
       </c>
       <c r="B18" t="n">
         <v>90562</v>
@@ -2559,10 +2545,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>566783</v>
+        <v>566899</v>
       </c>
       <c r="R18" t="n">
-        <v>7040615</v>
+        <v>7040618</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2594,7 +2580,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2604,7 +2590,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2619,22 +2605,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120204829</v>
+        <v>120204419</v>
       </c>
       <c r="B19" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2647,34 +2633,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>566806</v>
+        <v>566839</v>
       </c>
       <c r="R19" t="n">
-        <v>7040686</v>
+        <v>7040579</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2706,7 +2697,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2716,7 +2707,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2731,19 +2722,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120204035</v>
+        <v>120204669</v>
       </c>
       <c r="B20" t="n">
         <v>57310</v>
@@ -2783,10 +2774,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>566792</v>
+        <v>566938</v>
       </c>
       <c r="R20" t="n">
-        <v>7040454</v>
+        <v>7040521</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2818,7 +2809,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2828,12 +2819,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2848,22 +2839,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120204143</v>
+        <v>120204747</v>
       </c>
       <c r="B21" t="n">
-        <v>57326</v>
+        <v>78526</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2876,39 +2867,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>566773</v>
+        <v>566894</v>
       </c>
       <c r="R21" t="n">
-        <v>7040502</v>
+        <v>7040615</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2940,7 +2926,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2950,7 +2936,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2965,22 +2951,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120204350</v>
+        <v>120204174</v>
       </c>
       <c r="B22" t="n">
-        <v>91005</v>
+        <v>97907</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2993,34 +2979,38 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>566788</v>
+        <v>566744</v>
       </c>
       <c r="R22" t="n">
-        <v>7040610</v>
+        <v>7040575</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3052,7 +3042,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3062,7 +3052,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3089,10 +3079,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120204659</v>
+        <v>120203654</v>
       </c>
       <c r="B23" t="n">
-        <v>90562</v>
+        <v>57310</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3105,34 +3095,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>566899</v>
+        <v>566693</v>
       </c>
       <c r="R23" t="n">
-        <v>7040618</v>
+        <v>7040577</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3164,7 +3159,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3174,7 +3169,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:28</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 40464-2024 artfynd.xlsx
+++ b/artfynd/A 40464-2024 artfynd.xlsx
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120203108</v>
+        <v>120204350</v>
       </c>
       <c r="B4" t="n">
-        <v>97907</v>
+        <v>91005</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,38 +920,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566673</v>
+        <v>566788</v>
       </c>
       <c r="R4" t="n">
-        <v>7040645</v>
+        <v>7040610</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -983,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120204350</v>
+        <v>120203108</v>
       </c>
       <c r="B5" t="n">
-        <v>91005</v>
+        <v>97907</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,34 +1032,38 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566788</v>
+        <v>566673</v>
       </c>
       <c r="R5" t="n">
-        <v>7040610</v>
+        <v>7040645</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1595,10 +1595,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120203880</v>
+        <v>120203415</v>
       </c>
       <c r="B10" t="n">
-        <v>90562</v>
+        <v>82305</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1611,21 +1611,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1635,10 +1635,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566742</v>
+        <v>566663</v>
       </c>
       <c r="R10" t="n">
-        <v>7040625</v>
+        <v>7040644</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1707,10 +1707,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120203415</v>
+        <v>120203880</v>
       </c>
       <c r="B11" t="n">
-        <v>82305</v>
+        <v>90562</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1723,21 +1723,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1747,10 +1747,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566663</v>
+        <v>566742</v>
       </c>
       <c r="R11" t="n">
-        <v>7040644</v>
+        <v>7040625</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1782,7 +1782,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1792,7 +1792,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 40464-2024 artfynd.xlsx
+++ b/artfynd/A 40464-2024 artfynd.xlsx
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120204350</v>
+        <v>120203108</v>
       </c>
       <c r="B4" t="n">
-        <v>91005</v>
+        <v>97907</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,34 +920,38 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566788</v>
+        <v>566673</v>
       </c>
       <c r="R4" t="n">
-        <v>7040610</v>
+        <v>7040645</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +993,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120203108</v>
+        <v>120204350</v>
       </c>
       <c r="B5" t="n">
-        <v>97907</v>
+        <v>91005</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,38 +1036,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566673</v>
+        <v>566788</v>
       </c>
       <c r="R5" t="n">
-        <v>7040645</v>
+        <v>7040610</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1595,10 +1595,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120203415</v>
+        <v>120203880</v>
       </c>
       <c r="B10" t="n">
-        <v>82305</v>
+        <v>90562</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1611,21 +1611,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1635,10 +1635,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566663</v>
+        <v>566742</v>
       </c>
       <c r="R10" t="n">
-        <v>7040644</v>
+        <v>7040625</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1707,10 +1707,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120203880</v>
+        <v>120203415</v>
       </c>
       <c r="B11" t="n">
-        <v>90562</v>
+        <v>82305</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1723,21 +1723,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1747,10 +1747,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566742</v>
+        <v>566663</v>
       </c>
       <c r="R11" t="n">
-        <v>7040625</v>
+        <v>7040644</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1782,7 +1782,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1792,7 +1792,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 40464-2024 artfynd.xlsx
+++ b/artfynd/A 40464-2024 artfynd.xlsx
@@ -1595,10 +1595,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120203880</v>
+        <v>120203415</v>
       </c>
       <c r="B10" t="n">
-        <v>90562</v>
+        <v>82305</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1611,21 +1611,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1635,10 +1635,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566742</v>
+        <v>566663</v>
       </c>
       <c r="R10" t="n">
-        <v>7040625</v>
+        <v>7040644</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1707,10 +1707,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120203415</v>
+        <v>120203880</v>
       </c>
       <c r="B11" t="n">
-        <v>82305</v>
+        <v>90562</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1723,21 +1723,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1747,10 +1747,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566663</v>
+        <v>566742</v>
       </c>
       <c r="R11" t="n">
-        <v>7040644</v>
+        <v>7040625</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1782,7 +1782,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1792,7 +1792,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 40464-2024 artfynd.xlsx
+++ b/artfynd/A 40464-2024 artfynd.xlsx
@@ -1595,10 +1595,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120203415</v>
+        <v>120203880</v>
       </c>
       <c r="B10" t="n">
-        <v>82305</v>
+        <v>90562</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1611,21 +1611,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1635,10 +1635,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566663</v>
+        <v>566742</v>
       </c>
       <c r="R10" t="n">
-        <v>7040644</v>
+        <v>7040625</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1707,10 +1707,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120203880</v>
+        <v>120203415</v>
       </c>
       <c r="B11" t="n">
-        <v>90562</v>
+        <v>82305</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1723,21 +1723,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1747,10 +1747,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566742</v>
+        <v>566663</v>
       </c>
       <c r="R11" t="n">
-        <v>7040625</v>
+        <v>7040644</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1782,7 +1782,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1792,7 +1792,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 40464-2024 artfynd.xlsx
+++ b/artfynd/A 40464-2024 artfynd.xlsx
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120203108</v>
+        <v>120204350</v>
       </c>
       <c r="B4" t="n">
-        <v>97907</v>
+        <v>91005</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,38 +920,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566673</v>
+        <v>566788</v>
       </c>
       <c r="R4" t="n">
-        <v>7040645</v>
+        <v>7040610</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -983,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120204350</v>
+        <v>120203108</v>
       </c>
       <c r="B5" t="n">
-        <v>91005</v>
+        <v>97907</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,34 +1032,38 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566788</v>
+        <v>566673</v>
       </c>
       <c r="R5" t="n">
-        <v>7040610</v>
+        <v>7040645</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 40464-2024 artfynd.xlsx
+++ b/artfynd/A 40464-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120204035</v>
+        <v>120204829</v>
       </c>
       <c r="B2" t="n">
-        <v>57310</v>
+        <v>78542</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566792</v>
+        <v>566806</v>
       </c>
       <c r="R2" t="n">
-        <v>7040454</v>
+        <v>7040686</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:45</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,22 +775,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120204829</v>
+        <v>120203108</v>
       </c>
       <c r="B3" t="n">
-        <v>78526</v>
+        <v>97930</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,38 +799,42 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566806</v>
+        <v>566673</v>
       </c>
       <c r="R3" t="n">
-        <v>7040686</v>
+        <v>7040645</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +876,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120204350</v>
+        <v>120203942</v>
       </c>
       <c r="B4" t="n">
-        <v>91005</v>
+        <v>57320</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,25 +915,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -944,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566788</v>
+        <v>566751</v>
       </c>
       <c r="R4" t="n">
-        <v>7040610</v>
+        <v>7040440</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +988,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,22 +1008,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120203108</v>
+        <v>120204143</v>
       </c>
       <c r="B5" t="n">
-        <v>97907</v>
+        <v>57336</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1028,30 +1032,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>5</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1060,10 +1065,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566673</v>
+        <v>566773</v>
       </c>
       <c r="R5" t="n">
-        <v>7040645</v>
+        <v>7040502</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1095,7 +1100,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,7 +1110,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1120,22 +1125,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120204731</v>
+        <v>120203772</v>
       </c>
       <c r="B6" t="n">
-        <v>90527</v>
+        <v>57336</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,38 +1149,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566899</v>
+        <v>566730</v>
       </c>
       <c r="R6" t="n">
-        <v>7040617</v>
+        <v>7040540</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1207,7 +1217,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1217,7 +1227,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1244,10 +1254,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120203942</v>
+        <v>120203518</v>
       </c>
       <c r="B7" t="n">
-        <v>57310</v>
+        <v>56524</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1260,16 +1270,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1278,16 +1288,21 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566751</v>
+        <v>566701</v>
       </c>
       <c r="R7" t="n">
-        <v>7040440</v>
+        <v>7040656</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1319,7 +1334,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1329,12 +1344,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:41</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1349,22 +1359,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120203518</v>
+        <v>120204659</v>
       </c>
       <c r="B8" t="n">
-        <v>56514</v>
+        <v>90580</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1377,39 +1387,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102612</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566701</v>
+        <v>566899</v>
       </c>
       <c r="R8" t="n">
-        <v>7040656</v>
+        <v>7040618</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1441,7 +1446,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1451,7 +1456,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1466,22 +1471,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120204143</v>
+        <v>120204350</v>
       </c>
       <c r="B9" t="n">
-        <v>57326</v>
+        <v>91023</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1490,43 +1495,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>566773</v>
+        <v>566788</v>
       </c>
       <c r="R9" t="n">
-        <v>7040502</v>
+        <v>7040610</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1558,7 +1558,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1583,22 +1583,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120203880</v>
+        <v>120203415</v>
       </c>
       <c r="B10" t="n">
-        <v>90562</v>
+        <v>82321</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1611,21 +1611,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1635,10 +1635,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566742</v>
+        <v>566663</v>
       </c>
       <c r="R10" t="n">
-        <v>7040625</v>
+        <v>7040644</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1707,10 +1707,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120203415</v>
+        <v>120204035</v>
       </c>
       <c r="B11" t="n">
-        <v>82305</v>
+        <v>57320</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1723,21 +1723,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1747,10 +1747,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566663</v>
+        <v>566792</v>
       </c>
       <c r="R11" t="n">
-        <v>7040644</v>
+        <v>7040454</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1782,7 +1782,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1792,7 +1792,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1807,22 +1812,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120204501</v>
+        <v>120203654</v>
       </c>
       <c r="B12" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1853,16 +1858,21 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566856</v>
+        <v>566693</v>
       </c>
       <c r="R12" t="n">
-        <v>7040544</v>
+        <v>7040577</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1894,7 +1904,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1904,12 +1914,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1924,22 +1934,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120204246</v>
+        <v>120204174</v>
       </c>
       <c r="B13" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1971,7 +1981,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1983,7 +1993,7 @@
         <v>566744</v>
       </c>
       <c r="R13" t="n">
-        <v>7040571</v>
+        <v>7040575</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2015,7 +2025,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2025,7 +2035,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2052,10 +2062,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120204481</v>
+        <v>120204246</v>
       </c>
       <c r="B14" t="n">
-        <v>78526</v>
+        <v>97930</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2064,35 +2074,39 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566855</v>
+        <v>566744</v>
       </c>
       <c r="R14" t="n">
         <v>7040571</v>
@@ -2127,7 +2141,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2137,7 +2151,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2167,7 +2181,7 @@
         <v>120204614</v>
       </c>
       <c r="B15" t="n">
-        <v>90580</v>
+        <v>90598</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2279,7 +2293,7 @@
         <v>120204371</v>
       </c>
       <c r="B16" t="n">
-        <v>90562</v>
+        <v>90580</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2388,10 +2402,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120203772</v>
+        <v>120204669</v>
       </c>
       <c r="B17" t="n">
-        <v>57326</v>
+        <v>57320</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2404,16 +2418,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2422,21 +2436,16 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>566730</v>
+        <v>566938</v>
       </c>
       <c r="R17" t="n">
-        <v>7040540</v>
+        <v>7040521</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2468,7 +2477,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2478,7 +2487,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2493,22 +2507,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120204659</v>
+        <v>120203880</v>
       </c>
       <c r="B18" t="n">
-        <v>90562</v>
+        <v>90580</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2545,10 +2559,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>566899</v>
+        <v>566742</v>
       </c>
       <c r="R18" t="n">
-        <v>7040618</v>
+        <v>7040625</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2580,7 +2594,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2590,7 +2604,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2605,22 +2619,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120204419</v>
+        <v>120204481</v>
       </c>
       <c r="B19" t="n">
-        <v>57310</v>
+        <v>78542</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2633,39 +2647,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>566839</v>
+        <v>566855</v>
       </c>
       <c r="R19" t="n">
-        <v>7040579</v>
+        <v>7040571</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2697,7 +2706,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2707,7 +2716,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2722,22 +2731,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120204669</v>
+        <v>120204419</v>
       </c>
       <c r="B20" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2768,16 +2777,21 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>566938</v>
+        <v>566839</v>
       </c>
       <c r="R20" t="n">
-        <v>7040521</v>
+        <v>7040579</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2809,7 +2823,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2819,12 +2833,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:36</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2839,12 +2848,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2854,7 +2863,7 @@
         <v>120204747</v>
       </c>
       <c r="B21" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2963,10 +2972,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120204174</v>
+        <v>120204501</v>
       </c>
       <c r="B22" t="n">
-        <v>97907</v>
+        <v>57320</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2975,42 +2984,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>566744</v>
+        <v>566856</v>
       </c>
       <c r="R22" t="n">
-        <v>7040575</v>
+        <v>7040544</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3042,7 +3047,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3052,7 +3057,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3079,10 +3089,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120203654</v>
+        <v>120204731</v>
       </c>
       <c r="B23" t="n">
-        <v>57310</v>
+        <v>90545</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3091,43 +3101,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>566693</v>
+        <v>566899</v>
       </c>
       <c r="R23" t="n">
-        <v>7040577</v>
+        <v>7040617</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3159,7 +3164,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3169,12 +3174,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:28</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 40464-2024 artfynd.xlsx
+++ b/artfynd/A 40464-2024 artfynd.xlsx
@@ -1371,10 +1371,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120204659</v>
+        <v>120204035</v>
       </c>
       <c r="B8" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1387,21 +1387,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1411,10 +1411,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566899</v>
+        <v>566792</v>
       </c>
       <c r="R8" t="n">
-        <v>7040618</v>
+        <v>7040454</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1446,7 +1446,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1456,7 +1456,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1483,10 +1488,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120204350</v>
+        <v>120204659</v>
       </c>
       <c r="B9" t="n">
-        <v>91023</v>
+        <v>90580</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1495,25 +1500,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1523,10 +1528,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>566788</v>
+        <v>566899</v>
       </c>
       <c r="R9" t="n">
-        <v>7040610</v>
+        <v>7040618</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1558,7 +1563,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1568,7 +1573,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1583,22 +1588,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120203415</v>
+        <v>120204350</v>
       </c>
       <c r="B10" t="n">
-        <v>82321</v>
+        <v>91023</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1607,25 +1612,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1312</v>
+        <v>1209</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1635,10 +1640,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566663</v>
+        <v>566788</v>
       </c>
       <c r="R10" t="n">
-        <v>7040644</v>
+        <v>7040610</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1670,7 +1675,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1680,7 +1685,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1707,10 +1712,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120204035</v>
+        <v>120203415</v>
       </c>
       <c r="B11" t="n">
-        <v>57320</v>
+        <v>82321</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1723,21 +1728,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1747,10 +1752,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566792</v>
+        <v>566663</v>
       </c>
       <c r="R11" t="n">
-        <v>7040454</v>
+        <v>7040644</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1782,7 +1787,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1792,12 +1797,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:45</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1812,12 +1812,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 40464-2024 artfynd.xlsx
+++ b/artfynd/A 40464-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120204829</v>
+        <v>120204174</v>
       </c>
       <c r="B2" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,42 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566806</v>
+        <v>566744</v>
       </c>
       <c r="R2" t="n">
-        <v>7040686</v>
+        <v>7040575</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120203108</v>
+        <v>120204669</v>
       </c>
       <c r="B3" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,42 +803,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566673</v>
+        <v>566938</v>
       </c>
       <c r="R3" t="n">
-        <v>7040645</v>
+        <v>7040521</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +876,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120203942</v>
+        <v>120204614</v>
       </c>
       <c r="B4" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,21 +924,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -943,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566751</v>
+        <v>566938</v>
       </c>
       <c r="R4" t="n">
-        <v>7040440</v>
+        <v>7040520</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,12 +993,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:41</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,22 +1008,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120204143</v>
+        <v>120204659</v>
       </c>
       <c r="B5" t="n">
-        <v>57336</v>
+        <v>90580</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,39 +1036,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566773</v>
+        <v>566899</v>
       </c>
       <c r="R5" t="n">
-        <v>7040502</v>
+        <v>7040618</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,7 +1095,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1110,7 +1105,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1137,10 +1132,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120203772</v>
+        <v>120203415</v>
       </c>
       <c r="B6" t="n">
-        <v>57336</v>
+        <v>82321</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1153,39 +1148,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566730</v>
+        <v>566663</v>
       </c>
       <c r="R6" t="n">
-        <v>7040540</v>
+        <v>7040644</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1217,7 +1207,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1227,7 +1217,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1242,12 +1232,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1371,7 +1361,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120204035</v>
+        <v>120204501</v>
       </c>
       <c r="B8" t="n">
         <v>57320</v>
@@ -1411,10 +1401,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566792</v>
+        <v>566856</v>
       </c>
       <c r="R8" t="n">
-        <v>7040454</v>
+        <v>7040544</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1446,7 +1436,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1456,12 +1446,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1476,22 +1466,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120204659</v>
+        <v>120203108</v>
       </c>
       <c r="B9" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1500,38 +1490,42 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>566899</v>
+        <v>566673</v>
       </c>
       <c r="R9" t="n">
-        <v>7040618</v>
+        <v>7040645</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1563,7 +1557,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1573,7 +1567,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1588,22 +1582,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120204350</v>
+        <v>120204747</v>
       </c>
       <c r="B10" t="n">
-        <v>91023</v>
+        <v>78542</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1612,25 +1606,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1640,10 +1634,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566788</v>
+        <v>566894</v>
       </c>
       <c r="R10" t="n">
-        <v>7040610</v>
+        <v>7040615</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1675,7 +1669,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1685,7 +1679,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1712,10 +1706,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120203415</v>
+        <v>120204246</v>
       </c>
       <c r="B11" t="n">
-        <v>82321</v>
+        <v>97930</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1724,38 +1718,42 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566663</v>
+        <v>566744</v>
       </c>
       <c r="R11" t="n">
-        <v>7040644</v>
+        <v>7040571</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1787,7 +1785,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1797,7 +1795,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1824,10 +1822,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120203654</v>
+        <v>120204350</v>
       </c>
       <c r="B12" t="n">
-        <v>57320</v>
+        <v>91023</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1836,43 +1834,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566693</v>
+        <v>566788</v>
       </c>
       <c r="R12" t="n">
-        <v>7040577</v>
+        <v>7040610</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1904,7 +1897,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1914,12 +1907,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:28</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1934,22 +1922,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120204174</v>
+        <v>120203772</v>
       </c>
       <c r="B13" t="n">
-        <v>97930</v>
+        <v>57336</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1958,30 +1946,31 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>100</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1990,10 +1979,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566744</v>
+        <v>566730</v>
       </c>
       <c r="R13" t="n">
-        <v>7040575</v>
+        <v>7040540</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2025,7 +2014,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2035,7 +2024,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2050,22 +2039,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120204246</v>
+        <v>120204419</v>
       </c>
       <c r="B14" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2074,30 +2063,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2106,10 +2096,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566744</v>
+        <v>566839</v>
       </c>
       <c r="R14" t="n">
-        <v>7040571</v>
+        <v>7040579</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2141,7 +2131,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2151,7 +2141,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2166,22 +2156,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120204614</v>
+        <v>120204371</v>
       </c>
       <c r="B15" t="n">
-        <v>90598</v>
+        <v>90580</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2194,21 +2184,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2218,10 +2208,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>566938</v>
+        <v>566783</v>
       </c>
       <c r="R15" t="n">
-        <v>7040520</v>
+        <v>7040615</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2253,7 +2243,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2263,7 +2253,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2290,10 +2280,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120204371</v>
+        <v>120204481</v>
       </c>
       <c r="B16" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2306,21 +2296,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2330,10 +2320,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>566783</v>
+        <v>566855</v>
       </c>
       <c r="R16" t="n">
-        <v>7040615</v>
+        <v>7040571</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2365,7 +2355,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2375,7 +2365,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2402,10 +2392,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120204669</v>
+        <v>120204829</v>
       </c>
       <c r="B17" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2418,21 +2408,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2442,10 +2432,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>566938</v>
+        <v>566806</v>
       </c>
       <c r="R17" t="n">
-        <v>7040521</v>
+        <v>7040686</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2477,7 +2467,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2487,12 +2477,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:36</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2519,10 +2504,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120203880</v>
+        <v>120204035</v>
       </c>
       <c r="B18" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2535,21 +2520,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2559,10 +2544,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>566742</v>
+        <v>566792</v>
       </c>
       <c r="R18" t="n">
-        <v>7040625</v>
+        <v>7040454</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2594,7 +2579,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2604,7 +2589,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2619,22 +2609,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120204481</v>
+        <v>120203880</v>
       </c>
       <c r="B19" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2647,21 +2637,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2671,10 +2661,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>566855</v>
+        <v>566742</v>
       </c>
       <c r="R19" t="n">
-        <v>7040571</v>
+        <v>7040625</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2706,7 +2696,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2716,7 +2706,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2743,10 +2733,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120204419</v>
+        <v>120204143</v>
       </c>
       <c r="B20" t="n">
-        <v>57320</v>
+        <v>57336</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2759,16 +2749,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2779,7 +2769,7 @@
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2788,10 +2778,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>566839</v>
+        <v>566773</v>
       </c>
       <c r="R20" t="n">
-        <v>7040579</v>
+        <v>7040502</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2823,7 +2813,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2833,7 +2823,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2860,10 +2850,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120204747</v>
+        <v>120204731</v>
       </c>
       <c r="B21" t="n">
-        <v>78542</v>
+        <v>90545</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2872,25 +2862,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2900,10 +2890,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>566894</v>
+        <v>566899</v>
       </c>
       <c r="R21" t="n">
-        <v>7040615</v>
+        <v>7040617</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2935,7 +2925,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2945,7 +2935,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2960,19 +2950,19 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120204501</v>
+        <v>120203654</v>
       </c>
       <c r="B22" t="n">
         <v>57320</v>
@@ -3006,16 +2996,21 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>566856</v>
+        <v>566693</v>
       </c>
       <c r="R22" t="n">
-        <v>7040544</v>
+        <v>7040577</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3047,7 +3042,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3057,12 +3052,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3077,22 +3072,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120204731</v>
+        <v>120203942</v>
       </c>
       <c r="B23" t="n">
-        <v>90545</v>
+        <v>57320</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3101,25 +3096,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3129,10 +3124,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>566899</v>
+        <v>566751</v>
       </c>
       <c r="R23" t="n">
-        <v>7040617</v>
+        <v>7040440</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3164,7 +3159,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3174,7 +3169,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 40464-2024 artfynd.xlsx
+++ b/artfynd/A 40464-2024 artfynd.xlsx
@@ -2051,10 +2051,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120204419</v>
+        <v>120204371</v>
       </c>
       <c r="B14" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2067,39 +2067,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566839</v>
+        <v>566783</v>
       </c>
       <c r="R14" t="n">
-        <v>7040579</v>
+        <v>7040615</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2131,7 +2126,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2141,7 +2136,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2156,22 +2151,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120204371</v>
+        <v>120204419</v>
       </c>
       <c r="B15" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2184,34 +2179,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>566783</v>
+        <v>566839</v>
       </c>
       <c r="R15" t="n">
-        <v>7040615</v>
+        <v>7040579</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2268,12 +2268,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>

--- a/artfynd/A 40464-2024 artfynd.xlsx
+++ b/artfynd/A 40464-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120204174</v>
+        <v>120204659</v>
       </c>
       <c r="B2" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,42 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566744</v>
+        <v>566899</v>
       </c>
       <c r="R2" t="n">
-        <v>7040575</v>
+        <v>7040618</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,19 +775,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120204669</v>
+        <v>120204501</v>
       </c>
       <c r="B3" t="n">
         <v>57320</v>
@@ -831,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566938</v>
+        <v>566856</v>
       </c>
       <c r="R3" t="n">
-        <v>7040521</v>
+        <v>7040544</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -908,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120204614</v>
+        <v>120204350</v>
       </c>
       <c r="B4" t="n">
-        <v>90598</v>
+        <v>91023</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,25 +916,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -948,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566938</v>
+        <v>566788</v>
       </c>
       <c r="R4" t="n">
-        <v>7040520</v>
+        <v>7040610</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -983,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120204659</v>
+        <v>120204747</v>
       </c>
       <c r="B5" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,21 +1032,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1060,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566899</v>
+        <v>566894</v>
       </c>
       <c r="R5" t="n">
-        <v>7040618</v>
+        <v>7040615</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1095,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1120,22 +1116,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120203415</v>
+        <v>120203518</v>
       </c>
       <c r="B6" t="n">
-        <v>82321</v>
+        <v>56524</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1148,34 +1144,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>102612</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566663</v>
+        <v>566701</v>
       </c>
       <c r="R6" t="n">
-        <v>7040644</v>
+        <v>7040656</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1207,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1217,7 +1218,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1244,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120203518</v>
+        <v>120204174</v>
       </c>
       <c r="B7" t="n">
-        <v>56524</v>
+        <v>97930</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1256,31 +1257,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>100</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1289,10 +1289,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566701</v>
+        <v>566744</v>
       </c>
       <c r="R7" t="n">
-        <v>7040656</v>
+        <v>7040575</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1361,10 +1361,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120204501</v>
+        <v>120204143</v>
       </c>
       <c r="B8" t="n">
-        <v>57320</v>
+        <v>57336</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1377,16 +1377,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1395,16 +1395,21 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566856</v>
+        <v>566773</v>
       </c>
       <c r="R8" t="n">
-        <v>7040544</v>
+        <v>7040502</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1436,7 +1441,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1446,12 +1451,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:25</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1466,22 +1466,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120203108</v>
+        <v>120204829</v>
       </c>
       <c r="B9" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1490,42 +1490,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>566673</v>
+        <v>566806</v>
       </c>
       <c r="R9" t="n">
-        <v>7040645</v>
+        <v>7040686</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1557,7 +1553,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1567,7 +1563,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1594,10 +1590,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120204747</v>
+        <v>120204371</v>
       </c>
       <c r="B10" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1610,21 +1606,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1634,7 +1630,7 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566894</v>
+        <v>566783</v>
       </c>
       <c r="R10" t="n">
         <v>7040615</v>
@@ -1669,7 +1665,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1679,7 +1675,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1706,10 +1702,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120204246</v>
+        <v>120203880</v>
       </c>
       <c r="B11" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1718,42 +1714,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566744</v>
+        <v>566742</v>
       </c>
       <c r="R11" t="n">
-        <v>7040571</v>
+        <v>7040625</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1785,7 +1777,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1795,7 +1787,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1822,10 +1814,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120204350</v>
+        <v>120203772</v>
       </c>
       <c r="B12" t="n">
-        <v>91023</v>
+        <v>57336</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1834,38 +1826,43 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566788</v>
+        <v>566730</v>
       </c>
       <c r="R12" t="n">
-        <v>7040610</v>
+        <v>7040540</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1897,7 +1894,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1907,7 +1904,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1922,22 +1919,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120203772</v>
+        <v>120204419</v>
       </c>
       <c r="B13" t="n">
-        <v>57336</v>
+        <v>57320</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1950,16 +1947,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1970,7 +1967,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1979,10 +1976,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566730</v>
+        <v>566839</v>
       </c>
       <c r="R13" t="n">
-        <v>7040540</v>
+        <v>7040579</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2014,7 +2011,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2024,7 +2021,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2051,10 +2048,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120204371</v>
+        <v>120203108</v>
       </c>
       <c r="B14" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2063,38 +2060,42 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566783</v>
+        <v>566673</v>
       </c>
       <c r="R14" t="n">
-        <v>7040615</v>
+        <v>7040645</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2126,7 +2127,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2136,7 +2137,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2163,7 +2164,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120204419</v>
+        <v>120203942</v>
       </c>
       <c r="B15" t="n">
         <v>57320</v>
@@ -2197,21 +2198,16 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>566839</v>
+        <v>566751</v>
       </c>
       <c r="R15" t="n">
-        <v>7040579</v>
+        <v>7040440</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2243,7 +2239,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2253,7 +2249,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2280,10 +2281,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120204481</v>
+        <v>120204669</v>
       </c>
       <c r="B16" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2296,21 +2297,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2320,10 +2321,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>566855</v>
+        <v>566938</v>
       </c>
       <c r="R16" t="n">
-        <v>7040571</v>
+        <v>7040521</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2355,7 +2356,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2365,7 +2366,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2392,7 +2398,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120204829</v>
+        <v>120204481</v>
       </c>
       <c r="B17" t="n">
         <v>78542</v>
@@ -2432,10 +2438,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>566806</v>
+        <v>566855</v>
       </c>
       <c r="R17" t="n">
-        <v>7040686</v>
+        <v>7040571</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2467,7 +2473,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2477,7 +2483,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2504,10 +2510,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120204035</v>
+        <v>120204246</v>
       </c>
       <c r="B18" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2516,38 +2522,42 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>566792</v>
+        <v>566744</v>
       </c>
       <c r="R18" t="n">
-        <v>7040454</v>
+        <v>7040571</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2579,7 +2589,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2589,12 +2599,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:45</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2609,22 +2614,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120203880</v>
+        <v>120203415</v>
       </c>
       <c r="B19" t="n">
-        <v>90580</v>
+        <v>82321</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2637,21 +2642,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2661,10 +2666,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>566742</v>
+        <v>566663</v>
       </c>
       <c r="R19" t="n">
-        <v>7040625</v>
+        <v>7040644</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2696,7 +2701,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2706,7 +2711,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2733,10 +2738,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120204143</v>
+        <v>120203654</v>
       </c>
       <c r="B20" t="n">
-        <v>57336</v>
+        <v>57320</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2749,16 +2754,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2769,7 +2774,7 @@
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2778,10 +2783,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>566773</v>
+        <v>566693</v>
       </c>
       <c r="R20" t="n">
-        <v>7040502</v>
+        <v>7040577</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2813,7 +2818,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2823,7 +2828,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:28</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2850,10 +2860,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120204731</v>
+        <v>120204614</v>
       </c>
       <c r="B21" t="n">
-        <v>90545</v>
+        <v>90598</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2862,25 +2872,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2890,10 +2900,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>566899</v>
+        <v>566938</v>
       </c>
       <c r="R21" t="n">
-        <v>7040617</v>
+        <v>7040520</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2925,7 +2935,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2935,7 +2945,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2950,22 +2960,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120203654</v>
+        <v>120204731</v>
       </c>
       <c r="B22" t="n">
-        <v>57320</v>
+        <v>90545</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2974,43 +2984,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>566693</v>
+        <v>566899</v>
       </c>
       <c r="R22" t="n">
-        <v>7040577</v>
+        <v>7040617</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3042,7 +3047,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3052,12 +3057,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:28</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3084,7 +3084,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120203942</v>
+        <v>120204035</v>
       </c>
       <c r="B23" t="n">
         <v>57320</v>
@@ -3124,10 +3124,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>566751</v>
+        <v>566792</v>
       </c>
       <c r="R23" t="n">
-        <v>7040440</v>
+        <v>7040454</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3159,7 +3159,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 40464-2024 artfynd.xlsx
+++ b/artfynd/A 40464-2024 artfynd.xlsx
@@ -1702,10 +1702,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120203880</v>
+        <v>120203772</v>
       </c>
       <c r="B11" t="n">
-        <v>90580</v>
+        <v>57336</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1718,34 +1718,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566742</v>
+        <v>566730</v>
       </c>
       <c r="R11" t="n">
-        <v>7040625</v>
+        <v>7040540</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1777,7 +1782,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1787,7 +1792,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1802,22 +1807,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120203772</v>
+        <v>120204419</v>
       </c>
       <c r="B12" t="n">
-        <v>57336</v>
+        <v>57320</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1830,16 +1835,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1850,7 +1855,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1859,10 +1864,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566730</v>
+        <v>566839</v>
       </c>
       <c r="R12" t="n">
-        <v>7040540</v>
+        <v>7040579</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1894,7 +1899,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1904,7 +1909,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1931,10 +1936,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120204419</v>
+        <v>120203880</v>
       </c>
       <c r="B13" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1947,39 +1952,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566839</v>
+        <v>566742</v>
       </c>
       <c r="R13" t="n">
-        <v>7040579</v>
+        <v>7040625</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2021,7 +2021,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2036,22 +2036,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120203108</v>
+        <v>120204481</v>
       </c>
       <c r="B14" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2060,42 +2060,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566673</v>
+        <v>566855</v>
       </c>
       <c r="R14" t="n">
-        <v>7040645</v>
+        <v>7040571</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2127,7 +2123,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2137,7 +2133,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2398,10 +2394,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120204481</v>
+        <v>120203108</v>
       </c>
       <c r="B17" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2410,38 +2406,42 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>566855</v>
+        <v>566673</v>
       </c>
       <c r="R17" t="n">
-        <v>7040571</v>
+        <v>7040645</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 40464-2024 artfynd.xlsx
+++ b/artfynd/A 40464-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120204659</v>
+        <v>120203772</v>
       </c>
       <c r="B2" t="n">
-        <v>90580</v>
+        <v>57336</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566899</v>
+        <v>566730</v>
       </c>
       <c r="R2" t="n">
-        <v>7040618</v>
+        <v>7040540</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -904,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120204350</v>
+        <v>120204174</v>
       </c>
       <c r="B4" t="n">
-        <v>91023</v>
+        <v>97930</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,34 +925,38 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566788</v>
+        <v>566744</v>
       </c>
       <c r="R4" t="n">
-        <v>7040610</v>
+        <v>7040575</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +988,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +998,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1025,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120204747</v>
+        <v>120203108</v>
       </c>
       <c r="B5" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1028,38 +1037,42 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566894</v>
+        <v>566673</v>
       </c>
       <c r="R5" t="n">
-        <v>7040615</v>
+        <v>7040645</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,7 +1104,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1114,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,10 +1141,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120203518</v>
+        <v>120203415</v>
       </c>
       <c r="B6" t="n">
-        <v>56524</v>
+        <v>82321</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,39 +1157,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102612</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566701</v>
+        <v>566663</v>
       </c>
       <c r="R6" t="n">
-        <v>7040656</v>
+        <v>7040644</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1208,7 +1216,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1226,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,10 +1253,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120204174</v>
+        <v>120203942</v>
       </c>
       <c r="B7" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1257,42 +1265,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566744</v>
+        <v>566751</v>
       </c>
       <c r="R7" t="n">
-        <v>7040575</v>
+        <v>7040440</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1324,7 +1328,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1334,7 +1338,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1349,22 +1358,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120204143</v>
+        <v>120204747</v>
       </c>
       <c r="B8" t="n">
-        <v>57336</v>
+        <v>78542</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1377,39 +1386,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566773</v>
+        <v>566894</v>
       </c>
       <c r="R8" t="n">
-        <v>7040502</v>
+        <v>7040615</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1441,7 +1445,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1451,7 +1455,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1466,22 +1470,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120204829</v>
+        <v>120204614</v>
       </c>
       <c r="B9" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1494,21 +1498,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1518,10 +1522,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>566806</v>
+        <v>566938</v>
       </c>
       <c r="R9" t="n">
-        <v>7040686</v>
+        <v>7040520</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1553,7 +1557,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1563,7 +1567,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1590,10 +1594,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120204371</v>
+        <v>120204350</v>
       </c>
       <c r="B10" t="n">
-        <v>90580</v>
+        <v>91023</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1602,25 +1606,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1630,10 +1634,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566783</v>
+        <v>566788</v>
       </c>
       <c r="R10" t="n">
-        <v>7040615</v>
+        <v>7040610</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1665,7 +1669,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1675,7 +1679,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1702,10 +1706,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120203772</v>
+        <v>120203654</v>
       </c>
       <c r="B11" t="n">
-        <v>57336</v>
+        <v>57320</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1718,16 +1722,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1738,7 +1742,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1747,10 +1751,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566730</v>
+        <v>566693</v>
       </c>
       <c r="R11" t="n">
-        <v>7040540</v>
+        <v>7040577</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1782,7 +1786,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1792,7 +1796,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:28</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1819,10 +1828,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120204419</v>
+        <v>120203880</v>
       </c>
       <c r="B12" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1835,39 +1844,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566839</v>
+        <v>566742</v>
       </c>
       <c r="R12" t="n">
-        <v>7040579</v>
+        <v>7040625</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1899,7 +1903,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1909,7 +1913,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1924,19 +1928,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120203880</v>
+        <v>120204659</v>
       </c>
       <c r="B13" t="n">
         <v>90580</v>
@@ -1976,10 +1980,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566742</v>
+        <v>566899</v>
       </c>
       <c r="R13" t="n">
-        <v>7040625</v>
+        <v>7040618</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2011,7 +2015,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2021,7 +2025,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2036,22 +2040,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120204481</v>
+        <v>120204143</v>
       </c>
       <c r="B14" t="n">
-        <v>78542</v>
+        <v>57336</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2064,34 +2068,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566855</v>
+        <v>566773</v>
       </c>
       <c r="R14" t="n">
-        <v>7040571</v>
+        <v>7040502</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2123,7 +2132,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2133,7 +2142,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2148,22 +2157,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120203942</v>
+        <v>120204371</v>
       </c>
       <c r="B15" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2176,21 +2185,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2200,10 +2209,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>566751</v>
+        <v>566783</v>
       </c>
       <c r="R15" t="n">
-        <v>7040440</v>
+        <v>7040615</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2235,7 +2244,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2245,12 +2254,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:41</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2265,22 +2269,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120204669</v>
+        <v>120204481</v>
       </c>
       <c r="B16" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2293,21 +2297,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2317,10 +2321,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>566938</v>
+        <v>566855</v>
       </c>
       <c r="R16" t="n">
-        <v>7040521</v>
+        <v>7040571</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2352,7 +2356,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2362,12 +2366,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:36</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2394,10 +2393,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120203108</v>
+        <v>120204731</v>
       </c>
       <c r="B17" t="n">
-        <v>97930</v>
+        <v>90545</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2406,42 +2405,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>566673</v>
+        <v>566899</v>
       </c>
       <c r="R17" t="n">
-        <v>7040645</v>
+        <v>7040617</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2473,7 +2468,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2483,7 +2478,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2498,12 +2493,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2626,10 +2621,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120203415</v>
+        <v>120204035</v>
       </c>
       <c r="B19" t="n">
-        <v>82321</v>
+        <v>57320</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2642,21 +2637,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2666,10 +2661,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>566663</v>
+        <v>566792</v>
       </c>
       <c r="R19" t="n">
-        <v>7040644</v>
+        <v>7040454</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2701,7 +2696,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2711,7 +2706,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2726,22 +2726,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120203654</v>
+        <v>120204829</v>
       </c>
       <c r="B20" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2754,39 +2754,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>566693</v>
+        <v>566806</v>
       </c>
       <c r="R20" t="n">
-        <v>7040577</v>
+        <v>7040686</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2818,7 +2813,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2828,12 +2823,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:28</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2848,22 +2838,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120204614</v>
+        <v>120204669</v>
       </c>
       <c r="B21" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2876,21 +2866,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2903,7 +2893,7 @@
         <v>566938</v>
       </c>
       <c r="R21" t="n">
-        <v>7040520</v>
+        <v>7040521</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2935,7 +2925,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2945,7 +2935,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2972,10 +2967,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120204731</v>
+        <v>120204419</v>
       </c>
       <c r="B22" t="n">
-        <v>90545</v>
+        <v>57320</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2984,38 +2979,43 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>566899</v>
+        <v>566839</v>
       </c>
       <c r="R22" t="n">
-        <v>7040617</v>
+        <v>7040579</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3047,7 +3047,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3057,7 +3057,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3084,10 +3084,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120204035</v>
+        <v>120203518</v>
       </c>
       <c r="B23" t="n">
-        <v>57320</v>
+        <v>56524</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3100,16 +3100,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3118,16 +3118,21 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>566792</v>
+        <v>566701</v>
       </c>
       <c r="R23" t="n">
-        <v>7040454</v>
+        <v>7040656</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3159,7 +3164,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3169,12 +3174,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:45</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3189,12 +3189,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>

--- a/artfynd/A 40464-2024 artfynd.xlsx
+++ b/artfynd/A 40464-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120203772</v>
+        <v>120203518</v>
       </c>
       <c r="B2" t="n">
-        <v>57336</v>
+        <v>56524</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>102612</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -711,7 +711,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566730</v>
+        <v>566701</v>
       </c>
       <c r="R2" t="n">
-        <v>7040540</v>
+        <v>7040656</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,19 +780,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120204501</v>
+        <v>120203654</v>
       </c>
       <c r="B3" t="n">
         <v>57320</v>
@@ -826,16 +826,21 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566856</v>
+        <v>566693</v>
       </c>
       <c r="R3" t="n">
-        <v>7040544</v>
+        <v>7040577</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +882,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,12 +902,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1025,10 +1030,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120203108</v>
+        <v>120203772</v>
       </c>
       <c r="B5" t="n">
-        <v>97930</v>
+        <v>57336</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,30 +1042,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>5</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1069,10 +1075,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566673</v>
+        <v>566730</v>
       </c>
       <c r="R5" t="n">
-        <v>7040645</v>
+        <v>7040540</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1104,7 +1110,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1114,7 +1120,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1129,22 +1135,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120203415</v>
+        <v>120204371</v>
       </c>
       <c r="B6" t="n">
-        <v>82321</v>
+        <v>90580</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1157,21 +1163,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1181,10 +1187,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566663</v>
+        <v>566783</v>
       </c>
       <c r="R6" t="n">
-        <v>7040644</v>
+        <v>7040615</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1216,7 +1222,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1226,7 +1232,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1253,10 +1259,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120203942</v>
+        <v>120204731</v>
       </c>
       <c r="B7" t="n">
-        <v>57320</v>
+        <v>90545</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1265,25 +1271,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1293,10 +1299,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566751</v>
+        <v>566899</v>
       </c>
       <c r="R7" t="n">
-        <v>7040440</v>
+        <v>7040617</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1328,7 +1334,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1338,12 +1344,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:41</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1370,10 +1371,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120204747</v>
+        <v>120204143</v>
       </c>
       <c r="B8" t="n">
-        <v>78542</v>
+        <v>57336</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1386,34 +1387,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566894</v>
+        <v>566773</v>
       </c>
       <c r="R8" t="n">
-        <v>7040615</v>
+        <v>7040502</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1445,7 +1451,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1455,7 +1461,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1470,22 +1476,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120204614</v>
+        <v>120204350</v>
       </c>
       <c r="B9" t="n">
-        <v>90598</v>
+        <v>91023</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1494,25 +1500,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1522,10 +1528,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>566938</v>
+        <v>566788</v>
       </c>
       <c r="R9" t="n">
-        <v>7040520</v>
+        <v>7040610</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1557,7 +1563,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1567,7 +1573,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1594,10 +1600,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120204350</v>
+        <v>120203415</v>
       </c>
       <c r="B10" t="n">
-        <v>91023</v>
+        <v>82321</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1606,25 +1612,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1209</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1634,10 +1640,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566788</v>
+        <v>566663</v>
       </c>
       <c r="R10" t="n">
-        <v>7040610</v>
+        <v>7040644</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1669,7 +1675,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1679,7 +1685,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1706,10 +1712,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120203654</v>
+        <v>120204747</v>
       </c>
       <c r="B11" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1722,39 +1728,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566693</v>
+        <v>566894</v>
       </c>
       <c r="R11" t="n">
-        <v>7040577</v>
+        <v>7040615</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1786,7 +1787,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1796,12 +1797,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:28</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1816,22 +1812,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120203880</v>
+        <v>120204246</v>
       </c>
       <c r="B12" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1840,38 +1836,42 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566742</v>
+        <v>566744</v>
       </c>
       <c r="R12" t="n">
-        <v>7040625</v>
+        <v>7040571</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1903,7 +1903,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1940,10 +1940,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120204659</v>
+        <v>120204035</v>
       </c>
       <c r="B13" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1956,21 +1956,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566899</v>
+        <v>566792</v>
       </c>
       <c r="R13" t="n">
-        <v>7040618</v>
+        <v>7040454</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2025,7 +2025,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2052,10 +2057,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120204143</v>
+        <v>120203942</v>
       </c>
       <c r="B14" t="n">
-        <v>57336</v>
+        <v>57320</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2068,16 +2073,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2086,21 +2091,16 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566773</v>
+        <v>566751</v>
       </c>
       <c r="R14" t="n">
-        <v>7040502</v>
+        <v>7040440</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2142,7 +2142,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2169,10 +2174,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120204371</v>
+        <v>120204481</v>
       </c>
       <c r="B15" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2185,21 +2190,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2209,10 +2214,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>566783</v>
+        <v>566855</v>
       </c>
       <c r="R15" t="n">
-        <v>7040615</v>
+        <v>7040571</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2244,7 +2249,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2254,7 +2259,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2281,10 +2286,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120204481</v>
+        <v>120204501</v>
       </c>
       <c r="B16" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2297,21 +2302,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2321,10 +2326,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>566855</v>
+        <v>566856</v>
       </c>
       <c r="R16" t="n">
-        <v>7040571</v>
+        <v>7040544</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2356,7 +2361,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2366,7 +2371,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2393,10 +2403,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120204731</v>
+        <v>120203880</v>
       </c>
       <c r="B17" t="n">
-        <v>90545</v>
+        <v>90580</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2405,25 +2415,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2433,10 +2443,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>566899</v>
+        <v>566742</v>
       </c>
       <c r="R17" t="n">
-        <v>7040617</v>
+        <v>7040625</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2468,7 +2478,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2478,7 +2488,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2493,22 +2503,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120204246</v>
+        <v>120204669</v>
       </c>
       <c r="B18" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2517,42 +2527,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>566744</v>
+        <v>566938</v>
       </c>
       <c r="R18" t="n">
-        <v>7040571</v>
+        <v>7040521</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2584,7 +2590,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2594,7 +2600,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2621,7 +2632,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120204035</v>
+        <v>120204419</v>
       </c>
       <c r="B19" t="n">
         <v>57320</v>
@@ -2655,16 +2666,21 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>566792</v>
+        <v>566839</v>
       </c>
       <c r="R19" t="n">
-        <v>7040454</v>
+        <v>7040579</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2696,7 +2712,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2706,12 +2722,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:45</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2850,10 +2861,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120204669</v>
+        <v>120204614</v>
       </c>
       <c r="B21" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2866,21 +2877,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2893,7 +2904,7 @@
         <v>566938</v>
       </c>
       <c r="R21" t="n">
-        <v>7040521</v>
+        <v>7040520</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2925,7 +2936,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2935,12 +2946,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:36</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2967,10 +2973,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120204419</v>
+        <v>120204659</v>
       </c>
       <c r="B22" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2983,39 +2989,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>566839</v>
+        <v>566899</v>
       </c>
       <c r="R22" t="n">
-        <v>7040579</v>
+        <v>7040618</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3047,7 +3048,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3057,7 +3058,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3084,10 +3085,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120203518</v>
+        <v>120203108</v>
       </c>
       <c r="B23" t="n">
-        <v>56524</v>
+        <v>97930</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3096,31 +3097,30 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3129,10 +3129,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>566701</v>
+        <v>566673</v>
       </c>
       <c r="R23" t="n">
-        <v>7040656</v>
+        <v>7040645</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3164,7 +3164,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 40464-2024 artfynd.xlsx
+++ b/artfynd/A 40464-2024 artfynd.xlsx
@@ -2174,10 +2174,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120204481</v>
+        <v>120204501</v>
       </c>
       <c r="B15" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2190,21 +2190,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2214,10 +2214,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>566855</v>
+        <v>566856</v>
       </c>
       <c r="R15" t="n">
-        <v>7040571</v>
+        <v>7040544</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2249,7 +2249,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2259,7 +2259,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2286,10 +2291,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120204501</v>
+        <v>120204481</v>
       </c>
       <c r="B16" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2302,21 +2307,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2326,10 +2331,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>566856</v>
+        <v>566855</v>
       </c>
       <c r="R16" t="n">
-        <v>7040544</v>
+        <v>7040571</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2361,7 +2366,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2371,12 +2376,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:25</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 40464-2024 artfynd.xlsx
+++ b/artfynd/A 40464-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120203518</v>
+        <v>120203108</v>
       </c>
       <c r="B2" t="n">
-        <v>56524</v>
+        <v>97930</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566701</v>
+        <v>566673</v>
       </c>
       <c r="R2" t="n">
-        <v>7040656</v>
+        <v>7040645</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120203654</v>
+        <v>120204731</v>
       </c>
       <c r="B3" t="n">
-        <v>57320</v>
+        <v>90545</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,43 +803,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566693</v>
+        <v>566899</v>
       </c>
       <c r="R3" t="n">
-        <v>7040577</v>
+        <v>7040617</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,12 +876,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:28</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120204174</v>
+        <v>120204829</v>
       </c>
       <c r="B4" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -926,42 +915,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566744</v>
+        <v>566806</v>
       </c>
       <c r="R4" t="n">
-        <v>7040575</v>
+        <v>7040686</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,7 +988,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1030,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120203772</v>
+        <v>120204419</v>
       </c>
       <c r="B5" t="n">
-        <v>57336</v>
+        <v>57320</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1046,16 +1031,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1066,7 +1051,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1075,10 +1060,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566730</v>
+        <v>566839</v>
       </c>
       <c r="R5" t="n">
-        <v>7040540</v>
+        <v>7040579</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1110,7 +1095,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1120,7 +1105,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1147,10 +1132,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120204371</v>
+        <v>120204747</v>
       </c>
       <c r="B6" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1163,21 +1148,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1187,7 +1172,7 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566783</v>
+        <v>566894</v>
       </c>
       <c r="R6" t="n">
         <v>7040615</v>
@@ -1222,7 +1207,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1232,7 +1217,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1259,10 +1244,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120204731</v>
+        <v>120204035</v>
       </c>
       <c r="B7" t="n">
-        <v>90545</v>
+        <v>57320</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1271,25 +1256,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1299,10 +1284,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566899</v>
+        <v>566792</v>
       </c>
       <c r="R7" t="n">
-        <v>7040617</v>
+        <v>7040454</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1334,7 +1319,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1344,7 +1329,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1371,10 +1361,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120204143</v>
+        <v>120203518</v>
       </c>
       <c r="B8" t="n">
-        <v>57336</v>
+        <v>56524</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1387,16 +1377,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>102612</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1407,7 +1397,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1416,10 +1406,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566773</v>
+        <v>566701</v>
       </c>
       <c r="R8" t="n">
-        <v>7040502</v>
+        <v>7040656</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1451,7 +1441,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1461,7 +1451,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1476,12 +1466,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1600,10 +1590,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120203415</v>
+        <v>120204501</v>
       </c>
       <c r="B10" t="n">
-        <v>82321</v>
+        <v>57320</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1616,21 +1606,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1640,10 +1630,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566663</v>
+        <v>566856</v>
       </c>
       <c r="R10" t="n">
-        <v>7040644</v>
+        <v>7040544</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1675,7 +1665,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1685,7 +1675,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1712,7 +1707,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120204747</v>
+        <v>120204481</v>
       </c>
       <c r="B11" t="n">
         <v>78542</v>
@@ -1752,10 +1747,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566894</v>
+        <v>566855</v>
       </c>
       <c r="R11" t="n">
-        <v>7040615</v>
+        <v>7040571</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1787,7 +1782,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1797,7 +1792,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1824,10 +1819,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120204246</v>
+        <v>120204659</v>
       </c>
       <c r="B12" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1836,42 +1831,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566744</v>
+        <v>566899</v>
       </c>
       <c r="R12" t="n">
-        <v>7040571</v>
+        <v>7040618</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1903,7 +1894,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1913,7 +1904,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1928,19 +1919,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120204035</v>
+        <v>120203654</v>
       </c>
       <c r="B13" t="n">
         <v>57320</v>
@@ -1974,16 +1965,21 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566792</v>
+        <v>566693</v>
       </c>
       <c r="R13" t="n">
-        <v>7040454</v>
+        <v>7040577</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2015,7 +2011,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2025,7 +2021,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2057,7 +2053,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120203942</v>
+        <v>120204669</v>
       </c>
       <c r="B14" t="n">
         <v>57320</v>
@@ -2097,10 +2093,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566751</v>
+        <v>566938</v>
       </c>
       <c r="R14" t="n">
-        <v>7040440</v>
+        <v>7040521</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2132,7 +2128,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2142,12 +2138,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2162,22 +2158,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120204501</v>
+        <v>120204614</v>
       </c>
       <c r="B15" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2190,21 +2186,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2214,10 +2210,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>566856</v>
+        <v>566938</v>
       </c>
       <c r="R15" t="n">
-        <v>7040544</v>
+        <v>7040520</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2249,7 +2245,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2259,12 +2255,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:25</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2291,10 +2282,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120204481</v>
+        <v>120203942</v>
       </c>
       <c r="B16" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2307,21 +2298,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2331,10 +2322,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>566855</v>
+        <v>566751</v>
       </c>
       <c r="R16" t="n">
-        <v>7040571</v>
+        <v>7040440</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2366,7 +2357,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2376,7 +2367,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2391,12 +2387,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2515,10 +2511,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120204669</v>
+        <v>120204371</v>
       </c>
       <c r="B18" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2531,21 +2527,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2555,10 +2551,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>566938</v>
+        <v>566783</v>
       </c>
       <c r="R18" t="n">
-        <v>7040521</v>
+        <v>7040615</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2590,7 +2586,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2600,12 +2596,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:36</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2632,10 +2623,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120204419</v>
+        <v>120203772</v>
       </c>
       <c r="B19" t="n">
-        <v>57320</v>
+        <v>57336</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2648,16 +2639,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2668,7 +2659,7 @@
       <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2677,10 +2668,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>566839</v>
+        <v>566730</v>
       </c>
       <c r="R19" t="n">
-        <v>7040579</v>
+        <v>7040540</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2712,7 +2703,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2722,7 +2713,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2749,10 +2740,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120204829</v>
+        <v>120204246</v>
       </c>
       <c r="B20" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2761,38 +2752,42 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>566806</v>
+        <v>566744</v>
       </c>
       <c r="R20" t="n">
-        <v>7040686</v>
+        <v>7040571</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2824,7 +2819,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2834,7 +2829,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2861,10 +2856,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120204614</v>
+        <v>120204143</v>
       </c>
       <c r="B21" t="n">
-        <v>90598</v>
+        <v>57336</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2877,34 +2872,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>566938</v>
+        <v>566773</v>
       </c>
       <c r="R21" t="n">
-        <v>7040520</v>
+        <v>7040502</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2961,22 +2961,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120204659</v>
+        <v>120204174</v>
       </c>
       <c r="B22" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2985,38 +2985,42 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>566899</v>
+        <v>566744</v>
       </c>
       <c r="R22" t="n">
-        <v>7040618</v>
+        <v>7040575</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3048,7 +3052,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3058,7 +3062,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3073,22 +3077,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120203108</v>
+        <v>120203415</v>
       </c>
       <c r="B23" t="n">
-        <v>97930</v>
+        <v>82321</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3097,42 +3101,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>566673</v>
+        <v>566663</v>
       </c>
       <c r="R23" t="n">
-        <v>7040645</v>
+        <v>7040644</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3164,7 +3164,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 40464-2024 artfynd.xlsx
+++ b/artfynd/A 40464-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120203108</v>
+        <v>120204669</v>
       </c>
       <c r="B2" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,42 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566673</v>
+        <v>566938</v>
       </c>
       <c r="R2" t="n">
-        <v>7040645</v>
+        <v>7040521</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120204731</v>
+        <v>120204246</v>
       </c>
       <c r="B3" t="n">
-        <v>90545</v>
+        <v>97930</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,38 +804,42 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566899</v>
+        <v>566744</v>
       </c>
       <c r="R3" t="n">
-        <v>7040617</v>
+        <v>7040571</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,12 +896,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1015,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120204419</v>
+        <v>120204747</v>
       </c>
       <c r="B5" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1031,39 +1036,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566839</v>
+        <v>566894</v>
       </c>
       <c r="R5" t="n">
-        <v>7040579</v>
+        <v>7040615</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1120,22 +1120,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120204747</v>
+        <v>120203415</v>
       </c>
       <c r="B6" t="n">
-        <v>78542</v>
+        <v>82321</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1148,21 +1148,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1172,10 +1172,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566894</v>
+        <v>566663</v>
       </c>
       <c r="R6" t="n">
-        <v>7040615</v>
+        <v>7040644</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1244,10 +1244,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120204035</v>
+        <v>120204143</v>
       </c>
       <c r="B7" t="n">
-        <v>57320</v>
+        <v>57336</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1260,16 +1260,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1278,16 +1278,21 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566792</v>
+        <v>566773</v>
       </c>
       <c r="R7" t="n">
-        <v>7040454</v>
+        <v>7040502</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1319,7 +1324,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1329,12 +1334,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:45</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1361,10 +1361,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120203518</v>
+        <v>120203772</v>
       </c>
       <c r="B8" t="n">
-        <v>56524</v>
+        <v>57336</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1377,16 +1377,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1397,7 +1397,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1406,10 +1406,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566701</v>
+        <v>566730</v>
       </c>
       <c r="R8" t="n">
-        <v>7040656</v>
+        <v>7040540</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1441,7 +1441,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1466,22 +1466,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120204350</v>
+        <v>120203942</v>
       </c>
       <c r="B9" t="n">
-        <v>91023</v>
+        <v>57320</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1490,25 +1490,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1518,10 +1518,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>566788</v>
+        <v>566751</v>
       </c>
       <c r="R9" t="n">
-        <v>7040610</v>
+        <v>7040440</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1553,7 +1553,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1563,7 +1563,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1578,19 +1583,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120204501</v>
+        <v>120203654</v>
       </c>
       <c r="B10" t="n">
         <v>57320</v>
@@ -1624,16 +1629,21 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566856</v>
+        <v>566693</v>
       </c>
       <c r="R10" t="n">
-        <v>7040544</v>
+        <v>7040577</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1665,7 +1675,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1675,12 +1685,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1695,22 +1705,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120204481</v>
+        <v>120203108</v>
       </c>
       <c r="B11" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1719,38 +1729,42 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566855</v>
+        <v>566673</v>
       </c>
       <c r="R11" t="n">
-        <v>7040571</v>
+        <v>7040645</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1782,7 +1796,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1792,7 +1806,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1819,10 +1833,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120204659</v>
+        <v>120204174</v>
       </c>
       <c r="B12" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1831,38 +1845,42 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566899</v>
+        <v>566744</v>
       </c>
       <c r="R12" t="n">
-        <v>7040618</v>
+        <v>7040575</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1894,7 +1912,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1904,7 +1922,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1919,19 +1937,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120203654</v>
+        <v>120204419</v>
       </c>
       <c r="B13" t="n">
         <v>57320</v>
@@ -1976,10 +1994,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566693</v>
+        <v>566839</v>
       </c>
       <c r="R13" t="n">
-        <v>7040577</v>
+        <v>7040579</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2011,7 +2029,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2021,12 +2039,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:28</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2053,7 +2066,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120204669</v>
+        <v>120204501</v>
       </c>
       <c r="B14" t="n">
         <v>57320</v>
@@ -2093,10 +2106,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566938</v>
+        <v>566856</v>
       </c>
       <c r="R14" t="n">
-        <v>7040521</v>
+        <v>7040544</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2128,7 +2141,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2138,7 +2151,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2170,10 +2183,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120204614</v>
+        <v>120203880</v>
       </c>
       <c r="B15" t="n">
-        <v>90598</v>
+        <v>90580</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2186,21 +2199,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2210,10 +2223,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>566938</v>
+        <v>566742</v>
       </c>
       <c r="R15" t="n">
-        <v>7040520</v>
+        <v>7040625</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2245,7 +2258,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2255,7 +2268,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2282,10 +2295,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120203942</v>
+        <v>120204481</v>
       </c>
       <c r="B16" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2298,21 +2311,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2322,10 +2335,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>566751</v>
+        <v>566855</v>
       </c>
       <c r="R16" t="n">
-        <v>7040440</v>
+        <v>7040571</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2357,7 +2370,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2367,12 +2380,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:41</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2387,22 +2395,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120203880</v>
+        <v>120204035</v>
       </c>
       <c r="B17" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2415,21 +2423,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2439,10 +2447,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>566742</v>
+        <v>566792</v>
       </c>
       <c r="R17" t="n">
-        <v>7040625</v>
+        <v>7040454</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2474,7 +2482,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2484,7 +2492,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2499,19 +2512,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120204371</v>
+        <v>120204659</v>
       </c>
       <c r="B18" t="n">
         <v>90580</v>
@@ -2551,10 +2564,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>566783</v>
+        <v>566899</v>
       </c>
       <c r="R18" t="n">
-        <v>7040615</v>
+        <v>7040618</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2586,7 +2599,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2596,7 +2609,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2611,22 +2624,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120203772</v>
+        <v>120204614</v>
       </c>
       <c r="B19" t="n">
-        <v>57336</v>
+        <v>90598</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2639,39 +2652,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>566730</v>
+        <v>566938</v>
       </c>
       <c r="R19" t="n">
-        <v>7040540</v>
+        <v>7040520</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2703,7 +2711,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2713,7 +2721,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2728,22 +2736,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120204246</v>
+        <v>120203518</v>
       </c>
       <c r="B20" t="n">
-        <v>97930</v>
+        <v>56524</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2752,30 +2760,31 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2784,10 +2793,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>566744</v>
+        <v>566701</v>
       </c>
       <c r="R20" t="n">
-        <v>7040571</v>
+        <v>7040656</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2819,7 +2828,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2829,7 +2838,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2856,10 +2865,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120204143</v>
+        <v>120204350</v>
       </c>
       <c r="B21" t="n">
-        <v>57336</v>
+        <v>91023</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2868,43 +2877,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>566773</v>
+        <v>566788</v>
       </c>
       <c r="R21" t="n">
-        <v>7040502</v>
+        <v>7040610</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2936,7 +2940,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2946,7 +2950,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2961,22 +2965,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120204174</v>
+        <v>120204371</v>
       </c>
       <c r="B22" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2985,42 +2989,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>566744</v>
+        <v>566783</v>
       </c>
       <c r="R22" t="n">
-        <v>7040575</v>
+        <v>7040615</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3052,7 +3052,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3062,7 +3062,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3089,10 +3089,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120203415</v>
+        <v>120204731</v>
       </c>
       <c r="B23" t="n">
-        <v>82321</v>
+        <v>90545</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3101,25 +3101,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1312</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3129,10 +3129,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>566663</v>
+        <v>566899</v>
       </c>
       <c r="R23" t="n">
-        <v>7040644</v>
+        <v>7040617</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3164,7 +3164,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3189,12 +3189,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>

--- a/artfynd/A 40464-2024 artfynd.xlsx
+++ b/artfynd/A 40464-2024 artfynd.xlsx
@@ -1478,7 +1478,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120203942</v>
+        <v>120203654</v>
       </c>
       <c r="B9" t="n">
         <v>57320</v>
@@ -1512,16 +1512,21 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>566751</v>
+        <v>566693</v>
       </c>
       <c r="R9" t="n">
-        <v>7040440</v>
+        <v>7040577</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1553,7 +1558,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1563,12 +1568,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1595,7 +1600,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120203654</v>
+        <v>120203942</v>
       </c>
       <c r="B10" t="n">
         <v>57320</v>
@@ -1629,21 +1634,16 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566693</v>
+        <v>566751</v>
       </c>
       <c r="R10" t="n">
-        <v>7040577</v>
+        <v>7040440</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1685,12 +1685,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
